--- a/artfynd/A 66843-2020 artfynd.xlsx
+++ b/artfynd/A 66843-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178095</v>
+        <v>113178088</v>
       </c>
       <c r="B2" t="n">
-        <v>90043</v>
+        <v>90326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566778</v>
+        <v>566758</v>
       </c>
       <c r="R2" t="n">
-        <v>7027342</v>
+        <v>7027270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med grov gran</t>
+          <t>gles gammal barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
+          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178092</v>
+        <v>113178087</v>
       </c>
       <c r="B3" t="n">
-        <v>90689</v>
+        <v>90326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566615</v>
+        <v>566900</v>
       </c>
       <c r="R3" t="n">
-        <v>7027352</v>
+        <v>7027270</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +883,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178088</v>
+        <v>113178094</v>
       </c>
       <c r="B4" t="n">
-        <v>90310</v>
+        <v>90045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566758</v>
+        <v>566697</v>
       </c>
       <c r="R4" t="n">
-        <v>7027270</v>
+        <v>7027356</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +1002,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>gles gammal barrblandskog, naturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178093</v>
+        <v>113178091</v>
       </c>
       <c r="B5" t="n">
-        <v>90029</v>
+        <v>90063</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566629</v>
+        <v>566616</v>
       </c>
       <c r="R5" t="n">
-        <v>7027352</v>
+        <v>7027340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,15 +1121,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113178090</v>
+        <v>113178083</v>
       </c>
       <c r="B6" t="n">
-        <v>90029</v>
+        <v>90485</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,25 +1163,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566821</v>
+        <v>567028</v>
       </c>
       <c r="R6" t="n">
-        <v>7027337</v>
+        <v>7027267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,15 +1240,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>gammal grannaturskog med mycket gott om död ved</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113178091</v>
+        <v>113178090</v>
       </c>
       <c r="B7" t="n">
-        <v>90047</v>
+        <v>90045</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566616</v>
+        <v>566821</v>
       </c>
       <c r="R7" t="n">
-        <v>7027340</v>
+        <v>7027337</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,15 +1359,15 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113178089</v>
+        <v>113178095</v>
       </c>
       <c r="B8" t="n">
-        <v>90047</v>
+        <v>90059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
         <v>566778</v>
       </c>
       <c r="R8" t="n">
-        <v>7027315</v>
+        <v>7027342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med grov gran</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
+          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178085</v>
+        <v>113178086</v>
       </c>
       <c r="B9" t="n">
-        <v>90469</v>
+        <v>95186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,21 +1524,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
         <v>566908</v>
       </c>
       <c r="R9" t="n">
-        <v>7027266</v>
+        <v>7027263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
+          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
         <v>113178084</v>
       </c>
       <c r="B10" t="n">
-        <v>90310</v>
+        <v>90326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178087</v>
+        <v>113178092</v>
       </c>
       <c r="B11" t="n">
-        <v>90310</v>
+        <v>90705</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,25 +1758,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566900</v>
+        <v>566615</v>
       </c>
       <c r="R11" t="n">
-        <v>7027270</v>
+        <v>7027352</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,15 +1835,15 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113178094</v>
+        <v>113178089</v>
       </c>
       <c r="B12" t="n">
-        <v>90029</v>
+        <v>90063</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,21 +1881,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566697</v>
+        <v>566778</v>
       </c>
       <c r="R12" t="n">
-        <v>7027356</v>
+        <v>7027315</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1958,11 +1958,11 @@
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113178083</v>
+        <v>113178085</v>
       </c>
       <c r="B13" t="n">
-        <v>90469</v>
+        <v>90485</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567028</v>
+        <v>566908</v>
       </c>
       <c r="R13" t="n">
-        <v>7027267</v>
+        <v>7027266</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>gammal grannaturskog med mycket gott om död ved</t>
+          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
+          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113178086</v>
+        <v>113178093</v>
       </c>
       <c r="B14" t="n">
-        <v>95170</v>
+        <v>90045</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>990</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566908</v>
+        <v>566629</v>
       </c>
       <c r="R14" t="n">
-        <v>7027263</v>
+        <v>7027352</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2192,15 +2192,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 66843-2020 artfynd.xlsx
+++ b/artfynd/A 66843-2020 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178087</v>
+        <v>113178085</v>
       </c>
       <c r="B3" t="n">
-        <v>90326</v>
+        <v>90485</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566900</v>
+        <v>566908</v>
       </c>
       <c r="R3" t="n">
-        <v>7027270</v>
+        <v>7027266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +883,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
+          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178094</v>
+        <v>113178084</v>
       </c>
       <c r="B4" t="n">
-        <v>90045</v>
+        <v>90326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566697</v>
+        <v>566916</v>
       </c>
       <c r="R4" t="n">
-        <v>7027356</v>
+        <v>7027242</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +1002,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>hänglavsrik gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>6 substratenheter # e</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178091</v>
+        <v>113178093</v>
       </c>
       <c r="B5" t="n">
-        <v>90063</v>
+        <v>90045</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566616</v>
+        <v>566629</v>
       </c>
       <c r="R5" t="n">
-        <v>7027340</v>
+        <v>7027352</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,15 +1121,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113178083</v>
+        <v>113178087</v>
       </c>
       <c r="B6" t="n">
-        <v>90485</v>
+        <v>90326</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,25 +1163,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567028</v>
+        <v>566900</v>
       </c>
       <c r="R6" t="n">
-        <v>7027267</v>
+        <v>7027270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,15 +1240,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>gammal grannaturskog med mycket gott om död ved</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113178090</v>
+        <v>113178095</v>
       </c>
       <c r="B7" t="n">
-        <v>90045</v>
+        <v>90059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566821</v>
+        <v>566778</v>
       </c>
       <c r="R7" t="n">
-        <v>7027337</v>
+        <v>7027342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,15 +1359,15 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med grov gran</t>
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113178095</v>
+        <v>113178090</v>
       </c>
       <c r="B8" t="n">
-        <v>90059</v>
+        <v>90045</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566778</v>
+        <v>566821</v>
       </c>
       <c r="R8" t="n">
-        <v>7027342</v>
+        <v>7027337</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,15 +1478,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med grov gran</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178086</v>
+        <v>113178089</v>
       </c>
       <c r="B9" t="n">
-        <v>95186</v>
+        <v>90063</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,25 +1520,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>990</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566908</v>
+        <v>566778</v>
       </c>
       <c r="R9" t="n">
-        <v>7027263</v>
+        <v>7027315</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
+          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113178084</v>
+        <v>113178083</v>
       </c>
       <c r="B10" t="n">
-        <v>90326</v>
+        <v>90485</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566916</v>
+        <v>567028</v>
       </c>
       <c r="R10" t="n">
-        <v>7027242</v>
+        <v>7027267</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,15 +1716,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal barrnaturskog</t>
+          <t>gammal grannaturskog med mycket gott om död ved</t>
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>6 substratenheter # e</t>
+          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178092</v>
+        <v>113178091</v>
       </c>
       <c r="B11" t="n">
-        <v>90705</v>
+        <v>90063</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,25 +1758,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566615</v>
+        <v>566616</v>
       </c>
       <c r="R11" t="n">
-        <v>7027352</v>
+        <v>7027340</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113178089</v>
+        <v>113178094</v>
       </c>
       <c r="B12" t="n">
-        <v>90063</v>
+        <v>90045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,21 +1881,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566778</v>
+        <v>566697</v>
       </c>
       <c r="R12" t="n">
-        <v>7027315</v>
+        <v>7027356</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1958,11 +1958,11 @@
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113178085</v>
+        <v>113178092</v>
       </c>
       <c r="B13" t="n">
-        <v>90485</v>
+        <v>90705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566908</v>
+        <v>566615</v>
       </c>
       <c r="R13" t="n">
-        <v>7027266</v>
+        <v>7027352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113178093</v>
+        <v>113178086</v>
       </c>
       <c r="B14" t="n">
-        <v>90045</v>
+        <v>95186</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>990</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566629</v>
+        <v>566908</v>
       </c>
       <c r="R14" t="n">
-        <v>7027352</v>
+        <v>7027263</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2192,15 +2192,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 66843-2020 artfynd.xlsx
+++ b/artfynd/A 66843-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178088</v>
+        <v>113178095</v>
       </c>
       <c r="B2" t="n">
-        <v>90326</v>
+        <v>90071</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566758</v>
+        <v>566778</v>
       </c>
       <c r="R2" t="n">
-        <v>7027270</v>
+        <v>7027342</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>gles gammal barrblandskog, naturskog</t>
+          <t>olikåldrig grannaturskog med grov gran</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
+          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178085</v>
+        <v>113178094</v>
       </c>
       <c r="B3" t="n">
-        <v>90485</v>
+        <v>90057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566908</v>
+        <v>566697</v>
       </c>
       <c r="R3" t="n">
-        <v>7027266</v>
+        <v>7027356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +883,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178084</v>
+        <v>113178089</v>
       </c>
       <c r="B4" t="n">
-        <v>90326</v>
+        <v>90075</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566916</v>
+        <v>566778</v>
       </c>
       <c r="R4" t="n">
-        <v>7027242</v>
+        <v>7027315</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +1002,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal barrnaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>6 substratenheter # e</t>
+          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178093</v>
+        <v>113178091</v>
       </c>
       <c r="B5" t="n">
-        <v>90045</v>
+        <v>90075</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566629</v>
+        <v>566616</v>
       </c>
       <c r="R5" t="n">
-        <v>7027352</v>
+        <v>7027340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,15 +1121,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
         <v>113178087</v>
       </c>
       <c r="B6" t="n">
-        <v>90326</v>
+        <v>90338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113178095</v>
+        <v>113178088</v>
       </c>
       <c r="B7" t="n">
-        <v>90059</v>
+        <v>90338</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566778</v>
+        <v>566758</v>
       </c>
       <c r="R7" t="n">
-        <v>7027342</v>
+        <v>7027270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med grov gran</t>
+          <t>gles gammal barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
+          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113178090</v>
+        <v>113178093</v>
       </c>
       <c r="B8" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566821</v>
+        <v>566629</v>
       </c>
       <c r="R8" t="n">
-        <v>7027337</v>
+        <v>7027352</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178089</v>
+        <v>113178085</v>
       </c>
       <c r="B9" t="n">
-        <v>90063</v>
+        <v>90497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,25 +1520,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566778</v>
+        <v>566908</v>
       </c>
       <c r="R9" t="n">
-        <v>7027315</v>
+        <v>7027266</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
+          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
         <v>113178083</v>
       </c>
       <c r="B10" t="n">
-        <v>90485</v>
+        <v>90497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178091</v>
+        <v>113178084</v>
       </c>
       <c r="B11" t="n">
-        <v>90063</v>
+        <v>90338</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566616</v>
+        <v>566916</v>
       </c>
       <c r="R11" t="n">
-        <v>7027340</v>
+        <v>7027242</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,15 +1835,15 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>hänglavsrik gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>6 substratenheter # e</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113178094</v>
+        <v>113178092</v>
       </c>
       <c r="B12" t="n">
-        <v>90045</v>
+        <v>90717</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566697</v>
+        <v>566615</v>
       </c>
       <c r="R12" t="n">
-        <v>7027356</v>
+        <v>7027352</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1958,11 +1958,11 @@
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113178092</v>
+        <v>113178090</v>
       </c>
       <c r="B13" t="n">
-        <v>90705</v>
+        <v>90057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,25 +1996,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566615</v>
+        <v>566821</v>
       </c>
       <c r="R13" t="n">
-        <v>7027352</v>
+        <v>7027337</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,11 +2077,11 @@
         </is>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2106,7 +2106,7 @@
         <v>113178086</v>
       </c>
       <c r="B14" t="n">
-        <v>95186</v>
+        <v>95198</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 66843-2020 artfynd.xlsx
+++ b/artfynd/A 66843-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178095</v>
+        <v>113178092</v>
       </c>
       <c r="B2" t="n">
-        <v>90071</v>
+        <v>90717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566778</v>
+        <v>566615</v>
       </c>
       <c r="R2" t="n">
-        <v>7027342</v>
+        <v>7027352</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med grov gran</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178094</v>
+        <v>113178085</v>
       </c>
       <c r="B3" t="n">
-        <v>90057</v>
+        <v>90497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566697</v>
+        <v>566908</v>
       </c>
       <c r="R3" t="n">
-        <v>7027356</v>
+        <v>7027266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +883,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178089</v>
+        <v>113178084</v>
       </c>
       <c r="B4" t="n">
-        <v>90075</v>
+        <v>90338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566778</v>
+        <v>566916</v>
       </c>
       <c r="R4" t="n">
-        <v>7027315</v>
+        <v>7027242</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +1002,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>hänglavsrik gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
+          <t>6 substratenheter # e</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178091</v>
+        <v>113178095</v>
       </c>
       <c r="B5" t="n">
-        <v>90075</v>
+        <v>90071</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566616</v>
+        <v>566778</v>
       </c>
       <c r="R5" t="n">
-        <v>7027340</v>
+        <v>7027342</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>olikåldrig grannaturskog med grov gran</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113178087</v>
+        <v>113178083</v>
       </c>
       <c r="B6" t="n">
-        <v>90338</v>
+        <v>90497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,25 +1163,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566900</v>
+        <v>567028</v>
       </c>
       <c r="R6" t="n">
-        <v>7027270</v>
+        <v>7027267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,15 +1240,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>gammal grannaturskog med mycket gott om död ved</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
+          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113178088</v>
+        <v>113178094</v>
       </c>
       <c r="B7" t="n">
-        <v>90338</v>
+        <v>90057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566758</v>
+        <v>566697</v>
       </c>
       <c r="R7" t="n">
-        <v>7027270</v>
+        <v>7027356</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,15 +1359,15 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>gles gammal barrblandskog, naturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113178093</v>
+        <v>113178090</v>
       </c>
       <c r="B8" t="n">
         <v>90057</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566629</v>
+        <v>566821</v>
       </c>
       <c r="R8" t="n">
-        <v>7027352</v>
+        <v>7027337</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178085</v>
+        <v>113178087</v>
       </c>
       <c r="B9" t="n">
-        <v>90497</v>
+        <v>90338</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,25 +1520,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566908</v>
+        <v>566900</v>
       </c>
       <c r="R9" t="n">
-        <v>7027266</v>
+        <v>7027270</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,15 +1597,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113178083</v>
+        <v>113178088</v>
       </c>
       <c r="B10" t="n">
-        <v>90497</v>
+        <v>90338</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567028</v>
+        <v>566758</v>
       </c>
       <c r="R10" t="n">
-        <v>7027267</v>
+        <v>7027270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>gammal grannaturskog med mycket gott om död ved</t>
+          <t>gles gammal barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AN10" t="n">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
+          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178084</v>
+        <v>113178089</v>
       </c>
       <c r="B11" t="n">
-        <v>90338</v>
+        <v>90075</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566916</v>
+        <v>566778</v>
       </c>
       <c r="R11" t="n">
-        <v>7027242</v>
+        <v>7027315</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,15 +1835,15 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal barrnaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>6 substratenheter # e</t>
+          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113178092</v>
+        <v>113178091</v>
       </c>
       <c r="B12" t="n">
-        <v>90717</v>
+        <v>90075</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>898</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566615</v>
+        <v>566616</v>
       </c>
       <c r="R12" t="n">
-        <v>7027352</v>
+        <v>7027340</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113178090</v>
+        <v>113178093</v>
       </c>
       <c r="B13" t="n">
         <v>90057</v>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566821</v>
+        <v>566629</v>
       </c>
       <c r="R13" t="n">
-        <v>7027337</v>
+        <v>7027352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 66843-2020 artfynd.xlsx
+++ b/artfynd/A 66843-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178092</v>
+        <v>113178085</v>
       </c>
       <c r="B2" t="n">
-        <v>90717</v>
+        <v>90497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566615</v>
+        <v>566908</v>
       </c>
       <c r="R2" t="n">
-        <v>7027352</v>
+        <v>7027266</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178085</v>
+        <v>113178092</v>
       </c>
       <c r="B3" t="n">
-        <v>90497</v>
+        <v>90717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566908</v>
+        <v>566615</v>
       </c>
       <c r="R3" t="n">
-        <v>7027266</v>
+        <v>7027352</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,7 +883,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178095</v>
+        <v>113178083</v>
       </c>
       <c r="B5" t="n">
-        <v>90071</v>
+        <v>90497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566778</v>
+        <v>567028</v>
       </c>
       <c r="R5" t="n">
-        <v>7027342</v>
+        <v>7027267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med grov gran</t>
+          <t>gammal grannaturskog med mycket gott om död ved</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
+          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113178083</v>
+        <v>113178095</v>
       </c>
       <c r="B6" t="n">
-        <v>90497</v>
+        <v>90071</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,25 +1163,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567028</v>
+        <v>566778</v>
       </c>
       <c r="R6" t="n">
-        <v>7027267</v>
+        <v>7027342</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>gammal grannaturskog med mycket gott om död ved</t>
+          <t>olikåldrig grannaturskog med grov gran</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
+          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178087</v>
+        <v>113178089</v>
       </c>
       <c r="B9" t="n">
-        <v>90338</v>
+        <v>90075</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,21 +1524,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566900</v>
+        <v>566778</v>
       </c>
       <c r="R9" t="n">
-        <v>7027270</v>
+        <v>7027315</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,15 +1597,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
+          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113178088</v>
+        <v>113178087</v>
       </c>
       <c r="B10" t="n">
         <v>90338</v>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566758</v>
+        <v>566900</v>
       </c>
       <c r="R10" t="n">
         <v>7027270</v>
@@ -1716,15 +1716,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>gles gammal barrblandskog, naturskog</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178089</v>
+        <v>113178088</v>
       </c>
       <c r="B11" t="n">
-        <v>90075</v>
+        <v>90338</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566778</v>
+        <v>566758</v>
       </c>
       <c r="R11" t="n">
-        <v>7027315</v>
+        <v>7027270</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>gles gammal barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
+          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 66843-2020 artfynd.xlsx
+++ b/artfynd/A 66843-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178085</v>
+        <v>113178090</v>
       </c>
       <c r="B2" t="n">
-        <v>90497</v>
+        <v>90079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566908</v>
+        <v>566821</v>
       </c>
       <c r="R2" t="n">
-        <v>7027266</v>
+        <v>7027337</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,15 +764,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178092</v>
+        <v>113178093</v>
       </c>
       <c r="B3" t="n">
-        <v>90717</v>
+        <v>90079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566615</v>
+        <v>566629</v>
       </c>
       <c r="R3" t="n">
         <v>7027352</v>
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178084</v>
+        <v>113178092</v>
       </c>
       <c r="B4" t="n">
-        <v>90338</v>
+        <v>90739</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566916</v>
+        <v>566615</v>
       </c>
       <c r="R4" t="n">
-        <v>7027242</v>
+        <v>7027352</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +1002,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal barrnaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>6 substratenheter # e</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178083</v>
+        <v>113178084</v>
       </c>
       <c r="B5" t="n">
-        <v>90497</v>
+        <v>90360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,25 +1044,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567028</v>
+        <v>566916</v>
       </c>
       <c r="R5" t="n">
-        <v>7027267</v>
+        <v>7027242</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,15 +1121,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>gammal grannaturskog med mycket gott om död ved</t>
+          <t>hänglavsrik gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
+          <t>6 substratenheter # e</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
         <v>113178095</v>
       </c>
       <c r="B6" t="n">
-        <v>90071</v>
+        <v>90093</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113178094</v>
+        <v>113178085</v>
       </c>
       <c r="B7" t="n">
-        <v>90057</v>
+        <v>90519</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1282,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566697</v>
+        <v>566908</v>
       </c>
       <c r="R7" t="n">
-        <v>7027356</v>
+        <v>7027266</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,15 +1359,15 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113178090</v>
+        <v>113178094</v>
       </c>
       <c r="B8" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566821</v>
+        <v>566697</v>
       </c>
       <c r="R8" t="n">
-        <v>7027337</v>
+        <v>7027356</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178089</v>
+        <v>113178083</v>
       </c>
       <c r="B9" t="n">
-        <v>90075</v>
+        <v>90519</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,25 +1520,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566778</v>
+        <v>567028</v>
       </c>
       <c r="R9" t="n">
-        <v>7027315</v>
+        <v>7027267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>gammal grannaturskog med mycket gott om död ved</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
+          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
         <v>113178087</v>
       </c>
       <c r="B10" t="n">
-        <v>90338</v>
+        <v>90360</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178088</v>
+        <v>113178086</v>
       </c>
       <c r="B11" t="n">
-        <v>90338</v>
+        <v>95220</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,25 +1758,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566758</v>
+        <v>566908</v>
       </c>
       <c r="R11" t="n">
-        <v>7027270</v>
+        <v>7027263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>gles gammal barrblandskog, naturskog</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
+          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113178091</v>
+        <v>113178088</v>
       </c>
       <c r="B12" t="n">
-        <v>90075</v>
+        <v>90360</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,21 +1881,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566616</v>
+        <v>566758</v>
       </c>
       <c r="R12" t="n">
-        <v>7027340</v>
+        <v>7027270</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>gles gammal barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113178093</v>
+        <v>113178089</v>
       </c>
       <c r="B13" t="n">
-        <v>90057</v>
+        <v>90097</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2000,21 +2000,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566629</v>
+        <v>566778</v>
       </c>
       <c r="R13" t="n">
-        <v>7027352</v>
+        <v>7027315</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2077,11 +2077,11 @@
         </is>
       </c>
       <c r="AN13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113178086</v>
+        <v>113178091</v>
       </c>
       <c r="B14" t="n">
-        <v>95198</v>
+        <v>90097</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>990</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566908</v>
+        <v>566616</v>
       </c>
       <c r="R14" t="n">
-        <v>7027263</v>
+        <v>7027340</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN14" t="n">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 66843-2020 artfynd.xlsx
+++ b/artfynd/A 66843-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178090</v>
+        <v>113178087</v>
       </c>
       <c r="B2" t="n">
-        <v>90079</v>
+        <v>90364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566821</v>
+        <v>566900</v>
       </c>
       <c r="R2" t="n">
-        <v>7027337</v>
+        <v>7027270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178093</v>
+        <v>113178088</v>
       </c>
       <c r="B3" t="n">
-        <v>90079</v>
+        <v>90364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566629</v>
+        <v>566758</v>
       </c>
       <c r="R3" t="n">
-        <v>7027352</v>
+        <v>7027270</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +883,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>gles gammal barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178092</v>
+        <v>113178083</v>
       </c>
       <c r="B4" t="n">
-        <v>90739</v>
+        <v>90523</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566615</v>
+        <v>567028</v>
       </c>
       <c r="R4" t="n">
-        <v>7027352</v>
+        <v>7027267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>gammal grannaturskog med mycket gott om död ved</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178084</v>
+        <v>113178093</v>
       </c>
       <c r="B5" t="n">
-        <v>90360</v>
+        <v>90083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566916</v>
+        <v>566629</v>
       </c>
       <c r="R5" t="n">
-        <v>7027242</v>
+        <v>7027352</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,15 +1121,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal barrnaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>6 substratenheter # e</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113178095</v>
+        <v>113178090</v>
       </c>
       <c r="B6" t="n">
-        <v>90093</v>
+        <v>90083</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566778</v>
+        <v>566821</v>
       </c>
       <c r="R6" t="n">
-        <v>7027342</v>
+        <v>7027337</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,15 +1240,15 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med grov gran</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113178085</v>
+        <v>113178095</v>
       </c>
       <c r="B7" t="n">
-        <v>90519</v>
+        <v>90097</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1282,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566908</v>
+        <v>566778</v>
       </c>
       <c r="R7" t="n">
-        <v>7027266</v>
+        <v>7027342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med grov gran</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
+          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113178094</v>
+        <v>113178085</v>
       </c>
       <c r="B8" t="n">
-        <v>90079</v>
+        <v>90523</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566697</v>
+        <v>566908</v>
       </c>
       <c r="R8" t="n">
-        <v>7027356</v>
+        <v>7027266</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,15 +1478,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178083</v>
+        <v>113178092</v>
       </c>
       <c r="B9" t="n">
-        <v>90519</v>
+        <v>90743</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,21 +1524,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567028</v>
+        <v>566615</v>
       </c>
       <c r="R9" t="n">
-        <v>7027267</v>
+        <v>7027352</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>gammal grannaturskog med mycket gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113178087</v>
+        <v>113178089</v>
       </c>
       <c r="B10" t="n">
-        <v>90360</v>
+        <v>90101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,21 +1643,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566900</v>
+        <v>566778</v>
       </c>
       <c r="R10" t="n">
-        <v>7027270</v>
+        <v>7027315</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1716,15 +1716,15 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
+          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178086</v>
+        <v>113178091</v>
       </c>
       <c r="B11" t="n">
-        <v>95220</v>
+        <v>90101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,25 +1758,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>990</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566908</v>
+        <v>566616</v>
       </c>
       <c r="R11" t="n">
-        <v>7027263</v>
+        <v>7027340</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113178088</v>
+        <v>113178094</v>
       </c>
       <c r="B12" t="n">
-        <v>90360</v>
+        <v>90083</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,21 +1881,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566758</v>
+        <v>566697</v>
       </c>
       <c r="R12" t="n">
-        <v>7027270</v>
+        <v>7027356</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,15 +1954,15 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>gles gammal barrblandskog, naturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113178089</v>
+        <v>113178086</v>
       </c>
       <c r="B13" t="n">
-        <v>90097</v>
+        <v>95224</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,25 +1996,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>990</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566778</v>
+        <v>566908</v>
       </c>
       <c r="R13" t="n">
-        <v>7027315</v>
+        <v>7027263</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
+          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113178091</v>
+        <v>113178084</v>
       </c>
       <c r="B14" t="n">
-        <v>90097</v>
+        <v>90364</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566616</v>
+        <v>566916</v>
       </c>
       <c r="R14" t="n">
-        <v>7027340</v>
+        <v>7027242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2192,15 +2192,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>hänglavsrik gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>6 substratenheter # e</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 66843-2020 artfynd.xlsx
+++ b/artfynd/A 66843-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178087</v>
+        <v>113178089</v>
       </c>
       <c r="B2" t="n">
-        <v>90364</v>
+        <v>90101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566900</v>
+        <v>566778</v>
       </c>
       <c r="R2" t="n">
-        <v>7027270</v>
+        <v>7027315</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,15 +764,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
+          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178088</v>
+        <v>113178090</v>
       </c>
       <c r="B3" t="n">
-        <v>90364</v>
+        <v>90083</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566758</v>
+        <v>566821</v>
       </c>
       <c r="R3" t="n">
-        <v>7027270</v>
+        <v>7027337</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +883,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>gles gammal barrblandskog, naturskog</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113178083</v>
+        <v>113178093</v>
       </c>
       <c r="B4" t="n">
-        <v>90523</v>
+        <v>90083</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567028</v>
+        <v>566629</v>
       </c>
       <c r="R4" t="n">
-        <v>7027267</v>
+        <v>7027352</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,15 +1002,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>gammal grannaturskog med mycket gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178093</v>
+        <v>113178091</v>
       </c>
       <c r="B5" t="n">
-        <v>90083</v>
+        <v>90101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,21 +1048,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566629</v>
+        <v>566616</v>
       </c>
       <c r="R5" t="n">
-        <v>7027352</v>
+        <v>7027340</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,15 +1121,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # på levande gammal gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113178090</v>
+        <v>113178087</v>
       </c>
       <c r="B6" t="n">
-        <v>90083</v>
+        <v>90364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566821</v>
+        <v>566900</v>
       </c>
       <c r="R6" t="n">
-        <v>7027337</v>
+        <v>7027270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>2 substratenheter # grova förrötade granlågor av gammal gran</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113178095</v>
+        <v>113178092</v>
       </c>
       <c r="B7" t="n">
-        <v>90097</v>
+        <v>90743</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1282,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566778</v>
+        <v>566615</v>
       </c>
       <c r="R7" t="n">
-        <v>7027342</v>
+        <v>7027352</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med grov gran</t>
+          <t>olikåldrig grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
+          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113178085</v>
+        <v>113178088</v>
       </c>
       <c r="B8" t="n">
-        <v>90523</v>
+        <v>90364</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566908</v>
+        <v>566758</v>
       </c>
       <c r="R8" t="n">
-        <v>7027266</v>
+        <v>7027270</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
+          <t>gles gammal barrblandskog, naturskog</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
+          <t>1 substratenheter # förrötad granlåga av mycket gammal gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178092</v>
+        <v>113178095</v>
       </c>
       <c r="B9" t="n">
-        <v>90743</v>
+        <v>90097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,25 +1520,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566615</v>
+        <v>566778</v>
       </c>
       <c r="R9" t="n">
-        <v>7027352</v>
+        <v>7027342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig grannaturskog med grov gran</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # under murken förrötad granlåga med barken kvar, marknära</t>
+          <t>1 substratenheter # grov och äldre förrötad granlåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113178089</v>
+        <v>113178094</v>
       </c>
       <c r="B10" t="n">
-        <v>90101</v>
+        <v>90083</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,21 +1643,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566778</v>
+        <v>566697</v>
       </c>
       <c r="R10" t="n">
-        <v>7027315</v>
+        <v>7027356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,11 +1720,11 @@
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # stubbe och granlåga, förrötad av arten</t>
+          <t>2 substratenheter # grova förrötade granlågor</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178091</v>
+        <v>113178086</v>
       </c>
       <c r="B11" t="n">
-        <v>90101</v>
+        <v>95224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,25 +1758,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566616</v>
+        <v>566908</v>
       </c>
       <c r="R11" t="n">
-        <v>7027340</v>
+        <v>7027263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved, i kant mot kärr</t>
+          <t>hänglavsrik gammal grannaturskog</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # på levande gammal gran</t>
+          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113178094</v>
+        <v>113178085</v>
       </c>
       <c r="B12" t="n">
-        <v>90083</v>
+        <v>90523</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,25 +1877,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566697</v>
+        <v>566908</v>
       </c>
       <c r="R12" t="n">
-        <v>7027356</v>
+        <v>7027266</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,15 +1954,15 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>olikåldrig grannaturskog med gott om död ved</t>
+          <t>olikåldrig gammal grannaturskog med gott om död ved</t>
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova förrötade granlågor</t>
+          <t>1 substratenheter # förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113178086</v>
+        <v>113178084</v>
       </c>
       <c r="B13" t="n">
-        <v>95224</v>
+        <v>90364</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,25 +1996,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>990</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566908</v>
+        <v>566916</v>
       </c>
       <c r="R13" t="n">
-        <v>7027263</v>
+        <v>7027242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,15 +2073,15 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal grannaturskog</t>
+          <t>hänglavsrik gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad murken granlåga med intakt ytskikt</t>
+          <t>6 substratenheter # e</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113178084</v>
+        <v>113178083</v>
       </c>
       <c r="B14" t="n">
-        <v>90364</v>
+        <v>90523</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566916</v>
+        <v>567028</v>
       </c>
       <c r="R14" t="n">
-        <v>7027242</v>
+        <v>7027267</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2192,15 +2192,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>hänglavsrik gammal barrnaturskog</t>
+          <t>gammal grannaturskog med mycket gott om död ved</t>
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>6 substratenheter # e</t>
+          <t>1 substratenheter # grov förrötad granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 66843-2020 artfynd.xlsx
+++ b/artfynd/A 66843-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
